--- a/data/trans_orig/P32B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138440</t>
+          <t>137695</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146086</t>
+          <t>145215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65564</t>
+          <t>66936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208465</t>
+          <t>208330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217692</t>
+          <t>217720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>219982</t>
+          <t>219400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227886</t>
+          <t>227826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72751</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292086</t>
+          <t>292852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300559</t>
+          <t>300668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1419,97 +1419,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>191992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>279909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228130</t>
+          <t>228892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236923</t>
+          <t>236931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124995</t>
+          <t>124945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>358074</t>
+          <t>357166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367650</t>
+          <t>367367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,62 +2140,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92387</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138928</t>
+          <t>138099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185369</t>
+          <t>184070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103743</t>
+          <t>103723</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110836</t>
+          <t>110834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>294091</t>
+          <t>293730</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>304252</t>
+          <t>304161</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>287087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>421428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>486998</t>
+          <t>486958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231785</t>
+          <t>231993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239007</t>
+          <t>239020</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>723275</t>
+          <t>721923</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>731169</t>
+          <t>731069</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,82 +3492,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>18108</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>16469</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>36675</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>16261</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>15956</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>35383</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1855169</t>
+          <t>1855208</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1871384</t>
+          <t>1870699</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,82 +3605,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>876412</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>889937</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2737764</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2757970</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>878259</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>890459</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2739056</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2758483</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28209</t>
+          <t>28588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30323</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>147116</t>
+          <t>146737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>164586</t>
+          <t>163709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102206</t>
+          <t>102345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254694</t>
+          <t>254320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273339</t>
+          <t>272102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290772</t>
+          <t>290526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306205</t>
+          <t>306098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>443575</t>
+          <t>441698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>457632</t>
+          <t>457301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -4742,97 +4742,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1895</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>986</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5563</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200578</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202473</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321559</t>
+          <t>322164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,62 +5120,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4739</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186690</t>
+          <t>186323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273632</t>
+          <t>273694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>12152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116762</t>
+          <t>116056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126279</t>
+          <t>126283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54109</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171495</t>
+          <t>169900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180441</t>
+          <t>180322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,62 +5806,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178292</t>
+          <t>178109</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92244</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>272768</t>
+          <t>272726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8294</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>25798</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30464</t>
+          <t>29930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>371395</t>
+          <t>371671</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>389175</t>
+          <t>389557</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204903</t>
+          <t>205137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212517</t>
+          <t>212522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580464</t>
+          <t>580998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>600437</t>
+          <t>599948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>437785</t>
+          <t>437155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>449529</t>
+          <t>449636</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>208481</t>
+          <t>207962</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>649720</t>
+          <t>649750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>662741</t>
+          <t>662418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>44262</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74590</t>
+          <t>77238</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50990</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84477</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1967654</t>
+          <t>1965006</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1998742</t>
+          <t>1997982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1034300</t>
+          <t>1034215</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1045694</t>
+          <t>1045620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3006503</t>
+          <t>3008285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3039990</t>
+          <t>3041121</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>21633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>156787</t>
+          <t>157039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171365</t>
+          <t>171573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95718</t>
+          <t>95884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>104374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255107</t>
+          <t>256368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273870</t>
+          <t>274039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -7722,97 +7722,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>265731</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>267738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100259</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102259</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,62 +8100,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4352</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200127</t>
+          <t>199941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121576</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322339</t>
+          <t>322675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,62 +8443,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2225</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>8170</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6812</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>224484</t>
+          <t>225445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>150733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378496</t>
+          <t>377138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,82 +8751,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8648</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>3640</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>905</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1746</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>3640</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82697</t>
+          <t>82529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>119693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127688</t>
+          <t>127746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179472</t>
+          <t>179559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188102</t>
+          <t>188073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>99996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>284747</t>
+          <t>283758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292839</t>
+          <t>292751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>358676</t>
+          <t>359797</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>375397</t>
+          <t>375457</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240193</t>
+          <t>241289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251549</t>
+          <t>251592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>605647</t>
+          <t>607197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>624547</t>
+          <t>624964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,47 +9830,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>5611</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1938</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>5611</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>13617</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>443585</t>
+          <t>444098</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>454571</t>
+          <t>454576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>265268</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,47 +9943,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>716082</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>708440</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>719755</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>716082</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>708076</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>719841</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57266</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>69369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1945348</t>
+          <t>1943860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1971990</t>
+          <t>1972406</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1125470</t>
+          <t>1124933</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1138781</t>
+          <t>1138266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3076164</t>
+          <t>3077990</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3107528</t>
+          <t>3106429</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023 (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178397</t>
+          <t>178316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89989</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254241</t>
+          <t>255389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268964</t>
+          <t>268978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,62 +11080,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1526</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>15418</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3174</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>16047</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>235686</t>
+          <t>238434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115444</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355379</t>
+          <t>356008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169391</t>
+          <t>170575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181144</t>
+          <t>181545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85826</t>
+          <t>85385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89834</t>
+          <t>89826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258727</t>
+          <t>259091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270349</t>
+          <t>270505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172512</t>
+          <t>172497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121039</t>
+          <t>121324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295067</t>
+          <t>295828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301061</t>
+          <t>301316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -12074,97 +12074,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156761</t>
+          <t>156374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163643</t>
+          <t>163724</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>95868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249990</t>
+          <t>250668</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>258813</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>13141</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>25957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294521</t>
+          <t>294789</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304895</t>
+          <t>304879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380863</t>
+          <t>381130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398935</t>
+          <t>398844</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681621</t>
+          <t>681446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>702447</t>
+          <t>702394</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>269174</t>
+          <t>268602</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275864</t>
+          <t>275853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>93453</t>
+          <t>94757</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366486</t>
+          <t>366540</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374203</t>
+          <t>374085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,47 +13461,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>13525</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>23663</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>13525</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6984</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>24659</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1531526</t>
+          <t>1529215</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1556818</t>
+          <t>1556296</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,47 +13574,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1012322</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1002184</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1019922</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1012322</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1001188</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1018863</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2542255</t>
+          <t>2541718</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2573538</t>
+          <t>2574198</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137695</t>
+          <t>138427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145215</t>
+          <t>145239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66936</t>
+          <t>66796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208330</t>
+          <t>208257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217720</t>
+          <t>217718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>219400</t>
+          <t>219892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227826</t>
+          <t>227921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292852</t>
+          <t>292237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>300668</t>
+          <t>300568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228892</t>
+          <t>228435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>236931</t>
+          <t>236929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124945</t>
+          <t>125056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357166</t>
+          <t>356957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>367367</t>
+          <t>367363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>139735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>810</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>7974</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184070</t>
+          <t>184411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103723</t>
+          <t>103809</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110834</t>
+          <t>110973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>293730</t>
+          <t>293039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>486958</t>
+          <t>487787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231993</t>
+          <t>231845</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239020</t>
+          <t>239009</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>721923</t>
+          <t>722764</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>731069</t>
+          <t>731139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,82 +3492,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>17607</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>16605</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>36431</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>18108</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>36675</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1855208</t>
+          <t>1855499</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1870699</t>
+          <t>1871485</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,82 +3605,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>876913</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>889594</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2738008</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2757834</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>876412</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>889937</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2737764</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2757970</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12915</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>30043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146737</t>
+          <t>147596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163709</t>
+          <t>164203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102345</t>
+          <t>102317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254320</t>
+          <t>254974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272102</t>
+          <t>272298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>18482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>290526</t>
+          <t>292202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306098</t>
+          <t>306175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>441698</t>
+          <t>443000</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>457301</t>
+          <t>457625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119608</t>
+          <t>119630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322164</t>
+          <t>322274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186323</t>
+          <t>186429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273694</t>
+          <t>273103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116056</t>
+          <t>116880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126283</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>169900</t>
+          <t>170322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>180322</t>
+          <t>180318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178109</t>
+          <t>178547</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>272726</t>
+          <t>272747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10680</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>371671</t>
+          <t>372251</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>389557</t>
+          <t>389377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205137</t>
+          <t>204246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212522</t>
+          <t>212512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580998</t>
+          <t>580534</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>599948</t>
+          <t>600248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>15981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>437155</t>
+          <t>437769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>449636</t>
+          <t>449669</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>207962</t>
+          <t>208929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>649750</t>
+          <t>650008</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>662418</t>
+          <t>662573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>42163</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>77238</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>82695</t>
+          <t>84351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1965006</t>
+          <t>1966382</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1997982</t>
+          <t>2000081</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1034215</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1045620</t>
+          <t>1045635</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3008285</t>
+          <t>3006629</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3041121</t>
+          <t>3040777</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157039</t>
+          <t>155625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171573</t>
+          <t>171826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95884</t>
+          <t>95982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104374</t>
+          <t>104401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256368</t>
+          <t>255985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274039</t>
+          <t>273560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199941</t>
+          <t>200352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>322675</t>
+          <t>322393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225445</t>
+          <t>225425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377138</t>
+          <t>376732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82529</t>
+          <t>82655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>90292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119693</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127746</t>
+          <t>127724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179559</t>
+          <t>179265</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188073</t>
+          <t>188055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99996</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>283758</t>
+          <t>284039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292751</t>
+          <t>292782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>22841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>359797</t>
+          <t>359081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>375457</t>
+          <t>375474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>241289</t>
+          <t>240292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251592</t>
+          <t>251478</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>607197</t>
+          <t>605803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>624964</t>
+          <t>624079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>444098</t>
+          <t>442126</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>454576</t>
+          <t>454510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>708440</t>
+          <t>709345</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>719755</t>
+          <t>719754</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58754</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>69605</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1943860</t>
+          <t>1944884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1972406</t>
+          <t>1971385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1124933</t>
+          <t>1124430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1138266</t>
+          <t>1138533</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3077990</t>
+          <t>3077754</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3106429</t>
+          <t>3106400</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>174322</t>
+          <t>165698</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163533</t>
+          <t>159082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178316</t>
+          <t>168671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,27 +10845,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90517</t>
+          <t>96733</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>94210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>264838</t>
+          <t>262431</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255389</t>
+          <t>255012</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>268978</t>
+          <t>265868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -11120,12 +11120,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -11153,27 +11153,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>251282</t>
+          <t>255791</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238434</t>
+          <t>244214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11223,27 +11223,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>368252</t>
+          <t>378674</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356008</t>
+          <t>366974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>177333</t>
+          <t>177481</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>170116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181545</t>
+          <t>182221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88589</t>
+          <t>87498</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85385</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89826</t>
+          <t>88792</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>265922</t>
+          <t>264978</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259091</t>
+          <t>257058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270505</t>
+          <t>269749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -11839,27 +11839,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>175864</t>
+          <t>201081</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172497</t>
+          <t>196877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11874,27 +11874,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123443</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121324</t>
+          <t>134733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>299307</t>
+          <t>338468</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295828</t>
+          <t>334559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301316</t>
+          <t>340135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>177477</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>301822</t>
+          <t>341019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>161393</t>
+          <t>159484</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156374</t>
+          <t>155286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163724</t>
+          <t>161902</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>95963</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>255597</t>
+          <t>255446</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>250668</t>
+          <t>249781</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258813</t>
+          <t>258489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>301424</t>
+          <t>338191</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294789</t>
+          <t>326414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304879</t>
+          <t>343850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>392747</t>
+          <t>223987</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381130</t>
+          <t>213478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>398844</t>
+          <t>229809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>694171</t>
+          <t>562178</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>681446</t>
+          <t>549334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>702394</t>
+          <t>570444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>399473</t>
+          <t>233680</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707403</t>
+          <t>583385</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -13143,12 +13143,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4344</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>273932</t>
+          <t>310355</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>268602</t>
+          <t>305375</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275853</t>
+          <t>312459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,27 +13246,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>97709</t>
+          <t>112605</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94757</t>
+          <t>108770</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>371641</t>
+          <t>422962</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>366540</t>
+          <t>417294</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>374085</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>276512</t>
+          <t>313194</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99101</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>375612</t>
+          <t>427361</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>74234</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1546697</t>
+          <t>1642218</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1529215</t>
+          <t>1625235</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1556296</t>
+          <t>1653389</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1012322</t>
+          <t>887432</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1002184</t>
+          <t>874581</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1019922</t>
+          <t>894420</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2559019</t>
+          <t>2529650</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2541718</t>
+          <t>2508926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2574198</t>
+          <t>2542994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
